--- a/data/lookups/fonti_dati.xlsx
+++ b/data/lookups/fonti_dati.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\TOOLS\KNOWLEDGE SHARING\ProID\data\lookups\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCDC265D-B2C4-49AE-BB45-BAD46F45B306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEB96D16-415D-43F6-8157-A4DD9C10DD27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>value</t>
   </si>
@@ -106,6 +106,12 @@
   </si>
   <si>
     <t>AICA</t>
+  </si>
+  <si>
+    <t>Osservatorio del Mercato Immobiliare (OMI)</t>
+  </si>
+  <si>
+    <t>Agenzia delle Entrate</t>
   </si>
 </sst>
 </file>
@@ -404,134 +410,142 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>25</v>
+      <c r="A2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="5"/>
+    </row>
+    <row r="10" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="E9" s="5"/>
-    </row>
-    <row r="10" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" s="4"/>
     </row>
     <row r="17" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="3" t="s">
-        <v>13</v>
+      <c r="A19" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="2" t="s">
-        <v>15</v>
+      <c r="A21" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="29" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="30" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="31" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -1515,7 +1529,7 @@
     <row r="1009" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <autoFilter ref="A1:A22" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A26">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A28">
       <sortCondition ref="A1:A22"/>
     </sortState>
   </autoFilter>
